--- a/錢塘潮選股報告_2026-09-11.xlsx
+++ b/錢塘潮選股報告_2026-09-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,636 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>符合公式明細</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7072</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>F1_主力大買、F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1447</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕、F7_筆張現形</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20199</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2539</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>944</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9448</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8456</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>F1_主力大買、F2_一朵花</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>503</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2776</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>108</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10746</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>115</v>
+      </c>
+      <c r="C10" t="n">
+        <v>930</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>830</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>425</v>
+      </c>
+      <c r="C12" t="n">
+        <v>946</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F4_強力上</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>994</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18372</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>60965</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>205</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C16" t="n">
+        <v>26753</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>F1_主力大買、F7_筆張現形</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>495735</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>F2_一朵花、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>13861</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F3_主外上輕、F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6841</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>F1_主力大買、F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>65</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6788</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>F1_主力大買、F2_一朵花</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>363</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3612</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>82</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6214</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>12704</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6159</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>15976</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>F1_主力大買</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2821</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>F7_筆張現形</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>693</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>F5_洗盤後</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>6225</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1696</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>753</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="C30" t="n">
+        <v>144575</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>143176</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>F3_主外上輕</t>
         </is>
       </c>
     </row>
@@ -473,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +1121,84 @@
         <is>
           <t>今日成交量(張)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8456</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15976</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6841</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6788</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26753</v>
       </c>
     </row>
   </sheetData>
@@ -504,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +1230,123 @@
         <is>
           <t>今日成交量(張)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8456</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2539</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9448</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>108</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10746</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60965</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6788</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>495735</v>
       </c>
     </row>
   </sheetData>
@@ -535,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +1378,292 @@
         <is>
           <t>今日成交量(張)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>205</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12704</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2539</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>115</v>
+      </c>
+      <c r="C8" t="n">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>108</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10746</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6159</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>503</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60965</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>425</v>
+      </c>
+      <c r="C13" t="n">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>753</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6841</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6225</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>994</v>
+      </c>
+      <c r="C17" t="n">
+        <v>18372</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>13861</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>144575</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>495735</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>143176</v>
       </c>
     </row>
   </sheetData>
@@ -566,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +1695,19 @@
         <is>
           <t>今日成交量(張)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7799</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>425</v>
+      </c>
+      <c r="C2" t="n">
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +1739,136 @@
         <is>
           <t>今日成交量(張)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>363</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>205</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20199</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6214</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>115</v>
+      </c>
+      <c r="C6" t="n">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>503</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>469.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>994</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18372</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>13861</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +1913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,6 +1933,45 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26753</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
